--- a/CO国試data/CO_questions_2017.xlsx
+++ b/CO国試data/CO_questions_2017.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>免疫機構</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>True</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>免疫機構</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>True</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>True</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1289,12 +1281,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>感覚器</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1530,7 +1520,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1566,15 +1555,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1623,7 +1612,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1659,15 +1647,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1716,7 +1704,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1752,15 +1739,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -1850,15 +1837,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1907,7 +1894,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1943,15 +1929,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -2000,7 +1986,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2036,15 +2021,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -2093,7 +2078,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>False</t>
@@ -2129,15 +2113,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>1</v>
       </c>
@@ -2186,7 +2170,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2222,15 +2205,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>感覚器</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -2279,7 +2262,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2318,12 +2300,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -2372,7 +2354,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2411,12 +2392,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -2465,7 +2446,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2504,12 +2484,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -2558,7 +2538,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>True</t>
@@ -2594,15 +2573,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2651,7 +2630,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2687,15 +2665,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2744,7 +2722,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2780,15 +2757,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2837,7 +2814,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2873,15 +2849,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2930,7 +2906,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2966,15 +2941,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3023,7 +2998,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3059,15 +3033,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -3116,7 +3090,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3152,15 +3125,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3209,7 +3182,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3245,15 +3217,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3302,7 +3274,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3338,15 +3309,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3395,7 +3366,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>True</t>
@@ -3431,15 +3401,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3488,7 +3458,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3524,15 +3493,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3581,7 +3550,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3617,15 +3585,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3674,7 +3642,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3710,15 +3677,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -3767,7 +3734,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>True</t>
@@ -3803,15 +3769,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -3860,7 +3826,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3896,15 +3861,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3953,7 +3918,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -3989,15 +3953,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4046,7 +4010,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4082,15 +4045,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>1</v>
       </c>
@@ -4139,7 +4102,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4175,15 +4137,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4232,7 +4194,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4268,15 +4229,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4325,7 +4286,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>True</t>
@@ -4361,15 +4321,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>1</v>
       </c>
@@ -4418,7 +4378,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4454,15 +4413,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4511,7 +4470,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4547,15 +4505,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>4</v>
       </c>
@@ -4604,7 +4562,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4640,15 +4597,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4697,7 +4654,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4733,15 +4689,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4790,7 +4746,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4826,15 +4781,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>失明予防</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -4883,7 +4838,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4919,15 +4873,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4976,7 +4930,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>True</t>
@@ -5012,15 +4965,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5069,7 +5022,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5105,15 +5057,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5162,7 +5114,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>True</t>
@@ -5198,15 +5149,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -5256,7 +5207,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5292,15 +5242,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5349,7 +5299,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>True</t>
@@ -5385,15 +5334,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>1</v>
       </c>
@@ -5442,7 +5391,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5478,15 +5426,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5535,7 +5483,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5571,15 +5518,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5628,7 +5575,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>True</t>
@@ -5664,15 +5610,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5721,7 +5667,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>True</t>
@@ -5757,15 +5702,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>1</v>
       </c>
@@ -5814,7 +5759,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5850,15 +5794,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5907,7 +5851,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>True</t>
@@ -5943,15 +5886,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -6000,7 +5943,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6036,15 +5978,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6134,15 +6076,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6191,7 +6133,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6227,15 +6168,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6284,7 +6225,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6320,15 +6260,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6377,7 +6317,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6413,15 +6352,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6470,7 +6409,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6506,15 +6444,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6564,7 +6502,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6600,15 +6537,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6698,15 +6635,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6796,15 +6733,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6854,7 +6791,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>True</t>
@@ -6890,15 +6826,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -6948,7 +6884,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>False</t>
@@ -6984,15 +6919,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>2</v>
       </c>
@@ -7082,15 +7017,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>2</v>
       </c>
@@ -7180,15 +7115,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7238,7 +7173,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
           <t>True</t>
@@ -7274,15 +7208,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7372,15 +7306,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7470,15 +7404,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7568,15 +7502,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7625,7 +7559,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>True</t>
@@ -7661,15 +7594,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7718,7 +7651,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7754,15 +7686,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7811,7 +7743,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>True</t>
@@ -7847,15 +7778,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7904,7 +7835,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>True</t>
@@ -7940,15 +7870,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>心臓、血管</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7997,7 +7927,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8033,15 +7962,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -8090,7 +8019,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8126,15 +8054,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -8183,7 +8111,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8219,15 +8146,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8276,7 +8203,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8312,15 +8238,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8369,7 +8295,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8408,12 +8333,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>1</v>
       </c>
@@ -8462,7 +8387,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8498,15 +8422,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8555,7 +8479,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8591,15 +8514,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8648,7 +8571,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8684,15 +8606,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>1</v>
       </c>
@@ -8741,7 +8663,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8777,15 +8698,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8834,7 +8755,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8870,15 +8790,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8928,7 +8848,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8964,15 +8883,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9021,7 +8940,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>True</t>
@@ -9057,15 +8975,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9115,7 +9033,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9151,15 +9068,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9208,7 +9125,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9244,15 +9160,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9301,7 +9217,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9337,15 +9252,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>1</v>
       </c>
@@ -9394,7 +9309,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9430,15 +9344,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9487,7 +9401,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9523,15 +9436,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>1</v>
       </c>
@@ -9581,7 +9494,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9620,12 +9532,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9674,7 +9586,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>True</t>
@@ -9710,15 +9621,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>1</v>
       </c>
@@ -9767,7 +9678,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9803,15 +9713,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9860,7 +9770,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9896,15 +9805,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9953,7 +9862,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -9989,15 +9897,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10046,7 +9954,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10082,15 +9989,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10139,7 +10046,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10175,15 +10081,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10232,7 +10138,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>True</t>
@@ -10268,15 +10173,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10325,7 +10230,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10361,15 +10265,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10418,7 +10322,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10454,15 +10357,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10512,7 +10415,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>True</t>
@@ -10548,15 +10450,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10605,7 +10507,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>True</t>
@@ -10641,15 +10542,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>4</v>
       </c>
@@ -10698,7 +10599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10734,15 +10634,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10791,7 +10691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10827,15 +10726,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -10884,7 +10783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>True</t>
@@ -10920,15 +10818,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10977,7 +10875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>True</t>
@@ -11013,15 +10910,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11070,7 +10967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11106,15 +11002,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11163,7 +11059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11199,15 +11094,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11256,7 +11151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>True</t>
@@ -11292,15 +11186,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11349,7 +11243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>True</t>
@@ -11385,15 +11278,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>1</v>
       </c>
@@ -11442,7 +11335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11478,15 +11370,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11535,7 +11427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11571,15 +11462,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11628,7 +11519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11664,15 +11554,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11721,7 +11611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>True</t>
@@ -11757,15 +11646,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11814,7 +11703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11850,15 +11738,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11907,7 +11795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>True</t>
@@ -11943,15 +11830,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -12000,7 +11887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12036,15 +11922,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>1</v>
       </c>
@@ -12093,7 +11979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12129,15 +12014,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>1</v>
       </c>
@@ -12186,7 +12071,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>True</t>
@@ -12222,15 +12106,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12279,7 +12163,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12315,15 +12198,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12372,7 +12255,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12408,15 +12290,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>2</v>
       </c>
@@ -12465,7 +12347,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>True</t>
@@ -12501,15 +12382,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12558,7 +12439,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>True</t>
@@ -12594,15 +12474,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12651,7 +12531,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12687,15 +12566,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12744,7 +12623,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12780,15 +12658,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12837,7 +12715,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>True</t>
@@ -12873,15 +12750,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>4</v>
       </c>
@@ -12930,7 +12807,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -12966,15 +12842,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -13023,7 +12899,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13059,15 +12934,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13116,7 +12991,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13152,15 +13026,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13209,7 +13083,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>True</t>
@@ -13245,15 +13118,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>2</v>
       </c>
@@ -13302,7 +13175,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13338,15 +13210,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>2</v>
       </c>
@@ -13395,7 +13267,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13431,15 +13302,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>2</v>
       </c>
@@ -13488,7 +13359,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13524,15 +13394,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13581,7 +13451,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13617,15 +13486,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -13675,7 +13544,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
       <c r="S142" t="inlineStr">
         <is>
           <t>False</t>
@@ -13711,15 +13579,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>2</v>
       </c>
@@ -13769,7 +13637,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
           <t>False</t>
@@ -13805,15 +13672,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13903,15 +13770,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>2</v>
       </c>
@@ -13961,7 +13828,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr">
         <is>
           <t>False</t>
@@ -13997,15 +13863,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>2</v>
       </c>
@@ -14095,15 +13961,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>2</v>
       </c>
@@ -14193,15 +14059,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14291,15 +14157,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -14389,15 +14255,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14447,7 +14313,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
           <t>False</t>
@@ -14483,15 +14348,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2017.xlsx
+++ b/CO国試data/CO_questions_2017.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>免疫機構</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>免疫機構</t>
+          <t>免疫系の構成・機能</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>自律神経</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>免疫機構</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>免疫機構</t>
+          <t>免疫系の構成・機能</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>感覚器</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>感覚器</t>
+          <t>視覚系の構造と機能</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>感覚器</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>感覚器</t>
+          <t>視覚系の構造と機能</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>患者と視能訓練士の関係</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2849,12 +2849,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3309,12 +3309,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3493,12 +3493,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3769,12 +3769,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4229,12 +4229,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4597,12 +4597,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4689,12 +4689,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>失明予防</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>失明予防</t>
+          <t>予防と対策</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4873,12 +4873,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5242,12 +5242,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5702,12 +5702,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5794,12 +5794,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6168,12 +6168,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>光学的視能矯正</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6260,12 +6260,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6352,12 +6352,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>小児視能特性</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6537,12 +6537,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6826,12 +6826,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6919,12 +6919,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7017,12 +7017,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7115,12 +7115,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7208,12 +7208,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7306,12 +7306,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7404,12 +7404,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7502,12 +7502,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>末梢神経の構造と機能</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7778,12 +7778,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心臓、血管</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>心臓、血管</t>
+          <t>心臓、血管の構造と機能</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7962,12 +7962,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8330,12 +8330,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8422,12 +8422,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>屈折異常</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8883,12 +8883,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9068,12 +9068,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9252,12 +9252,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9344,12 +9344,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9713,12 +9713,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9897,12 +9897,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>固視検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10081,12 +10081,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10265,12 +10265,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10357,12 +10357,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10450,12 +10450,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10542,12 +10542,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10634,12 +10634,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10726,12 +10726,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10910,12 +10910,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11002,12 +11002,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11094,12 +11094,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11186,12 +11186,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11278,12 +11278,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11370,12 +11370,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11554,12 +11554,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11646,12 +11646,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11738,12 +11738,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11830,12 +11830,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11922,12 +11922,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>全身疾患と眼</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12014,12 +12014,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12198,12 +12198,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>眼位と眼球運動</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12290,12 +12290,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12474,12 +12474,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12566,12 +12566,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12658,12 +12658,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12750,12 +12750,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12842,12 +12842,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12934,12 +12934,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13118,12 +13118,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13210,12 +13210,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13394,12 +13394,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13486,12 +13486,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13579,12 +13579,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13770,12 +13770,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14255,12 +14255,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14348,12 +14348,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2017.xlsx
+++ b/CO国試data/CO_questions_2017.xlsx
@@ -550,7 +550,6 @@
           <t>免疫系の構成・機能</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -642,7 +641,11 @@
           <t>自律神経</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>副交感神経</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +737,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>染色体</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -826,7 +833,6 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +924,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1015,6 @@
           <t>免疫系の構成・機能</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1102,7 +1106,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1197,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>交感神経薬</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -1286,7 +1293,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1378,7 +1384,11 @@
           <t>視覚系の構造と機能</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>視神経、視交叉、視索、外側膝状体</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1470,7 +1480,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1563,7 +1577,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Panumの融像感覚圏</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1655,7 +1673,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>近見反応</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1747,7 +1769,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -1845,7 +1871,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>3</v>
       </c>
@@ -1937,7 +1967,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -2029,7 +2063,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -2121,7 +2154,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>1</v>
       </c>
@@ -2213,7 +2245,11 @@
           <t>視覚系の構造と機能</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>視神経、視交叉、視索、外側膝状体</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -2305,7 +2341,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -2397,7 +2432,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -2489,7 +2523,6 @@
           <t>患者と視能訓練士の関係</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -2581,7 +2614,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2673,7 +2710,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2765,7 +2801,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2857,7 +2897,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2949,7 +2993,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3041,7 +3084,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -3133,7 +3180,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3225,7 +3271,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3317,7 +3367,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3409,7 +3463,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3501,7 +3554,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>原発閉塞隅角緑内障</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3593,7 +3650,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3685,7 +3741,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -3777,7 +3832,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -3869,7 +3928,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>点眼薬</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -3961,7 +4024,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>眼瞼下垂</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4053,7 +4120,11 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>結膜炎</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>1</v>
       </c>
@@ -4145,7 +4216,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4237,7 +4307,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4329,7 +4398,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>瞳孔不同</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>1</v>
       </c>
@@ -4421,7 +4494,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4513,7 +4585,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
@@ -4605,7 +4681,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>他覚的屈折検査（波面収差解析を含む）</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4697,7 +4777,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4789,7 +4868,11 @@
           <t>予防と対策</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>失明（視能障害）原因疾患</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
@@ -4881,7 +4964,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4973,7 +5055,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5065,7 +5151,6 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5157,7 +5242,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>適応と方法</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -5250,7 +5339,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5342,7 +5435,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>1</v>
       </c>
@@ -5434,7 +5526,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5526,7 +5622,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5618,7 +5718,11 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>抑制除去訓練</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5710,7 +5814,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>1</v>
       </c>
@@ -5802,7 +5905,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5894,7 +5996,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -5986,7 +6087,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6084,7 +6184,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6176,7 +6280,11 @@
           <t>光学的視能矯正</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6268,7 +6376,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6360,7 +6467,6 @@
           <t>小児視能特性</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6452,7 +6558,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6545,7 +6650,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6643,7 +6752,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6741,7 +6854,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6834,7 +6946,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -6927,7 +7038,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>2</v>
       </c>
@@ -7025,7 +7135,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>2</v>
       </c>
@@ -7123,7 +7232,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7216,7 +7329,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7314,7 +7431,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7412,7 +7533,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7510,7 +7635,11 @@
           <t>末梢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>脳神経（第Ⅰ〜Ⅻ脳神経）</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7602,7 +7731,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7694,7 +7822,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>基本構造と機能</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7786,7 +7918,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7878,7 +8014,6 @@
           <t>心臓、血管の構造と機能</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -7970,7 +8105,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -8062,7 +8196,11 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>脳（大脳、間脳、中脳、橋、延髄、小脳）</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -8154,7 +8292,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -8246,7 +8383,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -8338,7 +8474,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>1</v>
       </c>
@@ -8430,7 +8565,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8522,7 +8661,6 @@
           <t>屈折異常</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8614,7 +8752,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
@@ -8706,7 +8848,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8798,7 +8944,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8891,7 +9036,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -8983,7 +9127,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9076,7 +9224,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9168,7 +9315,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -9260,7 +9411,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>1</v>
       </c>
@@ -9352,7 +9502,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9444,7 +9593,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>1</v>
       </c>
@@ -9537,7 +9685,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9629,7 +9776,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>1</v>
       </c>
@@ -9721,7 +9867,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9813,7 +9958,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9905,7 +10054,6 @@
           <t>固視検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -9997,7 +10145,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10089,7 +10241,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10181,7 +10337,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10273,7 +10433,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10365,7 +10524,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10458,7 +10621,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10550,7 +10717,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>4</v>
       </c>
@@ -10642,7 +10813,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>角膜内皮細胞検査</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -10734,7 +10909,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>3</v>
       </c>
@@ -10826,7 +11000,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10918,7 +11096,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11010,7 +11187,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11102,7 +11283,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11194,7 +11374,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11286,7 +11470,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>1</v>
       </c>
@@ -11378,7 +11561,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>角膜炎</t>
+        </is>
+      </c>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11470,7 +11657,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11562,7 +11748,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11654,7 +11839,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11746,7 +11935,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11838,7 +12026,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -11930,7 +12117,6 @@
           <t>全身疾患と眼</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>1</v>
       </c>
@@ -12022,7 +12208,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>1</v>
       </c>
@@ -12114,7 +12299,6 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12206,7 +12390,11 @@
           <t>眼位と眼球運動</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>眼位の異常</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12298,7 +12486,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>2</v>
       </c>
@@ -12390,7 +12577,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12482,7 +12673,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>斜視弱視</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12574,7 +12769,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12666,7 +12865,11 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>抑制除去訓練</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12758,7 +12961,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>4</v>
       </c>
@@ -12850,7 +13057,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>1</v>
       </c>
@@ -12942,7 +13148,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13034,7 +13244,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13126,7 +13335,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>2</v>
       </c>
@@ -13218,7 +13426,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>2</v>
       </c>
@@ -13310,7 +13517,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>2</v>
       </c>
@@ -13402,7 +13613,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13494,7 +13704,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -13587,7 +13801,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>2</v>
       </c>
@@ -13680,7 +13898,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13778,7 +14000,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>2</v>
       </c>
@@ -13871,7 +14092,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>2</v>
       </c>
@@ -13969,7 +14194,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>2</v>
       </c>
@@ -14067,7 +14291,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14165,7 +14388,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -14263,7 +14490,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14356,7 +14587,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>眼振の手術</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2017.xlsx
+++ b/CO国試data/CO_questions_2017.xlsx
@@ -598,10 +598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -694,10 +692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -790,10 +786,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -881,10 +875,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1250,10 +1242,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1341,10 +1331,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1437,10 +1425,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1534,10 +1520,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1630,10 +1614,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1726,10 +1708,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1828,10 +1808,8 @@
           <t>2017_co_17_am014.jpg</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1924,10 +1902,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2020,10 +1996,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2111,10 +2085,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2202,10 +2174,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2298,10 +2268,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2389,10 +2357,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2480,10 +2446,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2667,10 +2631,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2758,10 +2720,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2854,10 +2814,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2950,10 +2908,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3041,10 +2997,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3137,10 +3091,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3228,10 +3180,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3324,10 +3274,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3511,10 +3459,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3607,10 +3553,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3698,10 +3642,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3885,10 +3827,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3981,10 +3921,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4077,10 +4015,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4173,10 +4109,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4264,10 +4198,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4451,10 +4383,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4542,10 +4472,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4638,10 +4566,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4734,10 +4660,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4825,10 +4749,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4921,10 +4843,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5108,10 +5028,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5296,10 +5214,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5483,10 +5399,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5862,10 +5776,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5953,10 +5865,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6044,10 +5954,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6141,10 +6049,8 @@
           <t>2017_co_17_am060.jpg</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6237,10 +6143,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6333,10 +6237,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6424,10 +6326,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6515,10 +6415,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6607,10 +6505,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6811,10 +6707,8 @@
           <t>2017_co_17_am067.jpg</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6995,10 +6889,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7092,10 +6984,8 @@
           <t>2017_co_17_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7388,10 +7278,8 @@
           <t>2017_co_17_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7490,10 +7378,8 @@
           <t>2017_co_17_am074.jpg</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7688,10 +7574,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7779,10 +7663,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8062,10 +7944,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8153,10 +8033,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8249,10 +8127,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8340,10 +8216,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8431,10 +8305,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8522,10 +8394,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8618,10 +8488,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8709,10 +8577,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8805,10 +8671,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8901,10 +8765,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8993,10 +8855,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9084,10 +8944,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9181,10 +9039,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9272,10 +9128,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9368,10 +9222,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9459,10 +9311,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9550,10 +9400,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9642,10 +9490,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9824,10 +9670,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9915,10 +9759,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10011,10 +9853,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10102,10 +9942,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10198,10 +10036,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10294,10 +10130,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10390,10 +10224,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10481,10 +10313,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10674,10 +10504,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10770,10 +10598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10866,10 +10692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11144,10 +10968,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11240,10 +11062,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11427,10 +11247,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11518,10 +11336,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11614,10 +11430,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11705,10 +11519,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11892,10 +11704,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12074,10 +11884,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12165,10 +11973,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12347,10 +12153,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12443,10 +12247,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12630,10 +12432,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12726,10 +12526,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12822,10 +12620,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13014,10 +12810,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13105,10 +12899,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13383,10 +13175,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13474,10 +13264,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13570,10 +13358,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13661,10 +13447,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13758,10 +13542,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13855,10 +13637,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -13957,10 +13737,8 @@
           <t>2017_co_17_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14049,10 +13827,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14151,10 +13927,8 @@
           <t>2017_co_17_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14248,10 +14022,8 @@
           <t>2017_co_17_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14345,10 +14117,8 @@
           <t>2017_co_17_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14447,10 +14217,8 @@
           <t>2017_co_17_pm073.jpg;2017_co_17_pm073_2.jpg;2017_co_17_pm073_3.jpg;2017_co_17_pm073_4.jpg;2017_co_17_pm073_5.jpg;2017_co_17_pm073_6.jpg</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14544,10 +14312,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14646,10 +14412,8 @@
           <t>2017_co_17_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2017.xlsx
+++ b/CO国試data/CO_questions_2017.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -964,10 +964,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S6" t="b">
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1042,7 +1040,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1055,10 +1053,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S7" t="b">
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1133,7 +1129,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1146,10 +1142,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S8" t="b">
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2522,7 +2516,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2535,10 +2529,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S23" t="b">
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3355,7 +3347,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3368,10 +3360,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S32" t="b">
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3718,7 +3708,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3731,10 +3721,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S36" t="b">
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4274,7 +4262,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4287,10 +4275,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S42" t="b">
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4919,7 +4905,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4932,10 +4918,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S49" t="b">
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5104,7 +5088,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5117,10 +5101,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S51" t="b">
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5295,7 +5277,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5308,10 +5290,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S53" t="b">
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5480,7 +5460,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5493,10 +5473,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5576,7 +5554,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5589,10 +5567,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S56" t="b">
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5672,7 +5648,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5685,10 +5661,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S57" t="b">
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6130,7 +6104,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6144,7 +6118,7 @@
         </is>
       </c>
       <c r="S62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6587,7 +6561,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6605,10 +6579,8 @@
           <t>2017_co_17_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S67" t="b">
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6784,7 +6756,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6797,10 +6769,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S69" t="b">
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7061,7 +7031,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7079,10 +7049,8 @@
           <t>2017_co_17_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S72" t="b">
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7163,7 +7131,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7176,10 +7144,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S73" t="b">
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7460,7 +7426,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -7478,10 +7444,8 @@
           <t>2017_co_17_am075.jpg</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S76" t="b">
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7744,7 +7708,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -7757,10 +7721,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S79" t="b">
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7840,7 +7802,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7853,10 +7815,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S80" t="b">
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9566,7 +9526,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9579,10 +9539,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S99" t="b">
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10395,7 +10353,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10408,10 +10366,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S108" t="b">
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10768,7 +10724,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10781,10 +10737,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S112" t="b">
+        <v>1</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -10864,7 +10818,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10877,10 +10831,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S113" t="b">
+        <v>1</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11138,7 +11090,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11151,10 +11103,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S116" t="b">
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11780,7 +11730,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -11793,10 +11743,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S123" t="b">
+        <v>1</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12049,7 +11997,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12062,10 +12010,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S126" t="b">
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12323,7 +12269,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12336,10 +12282,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S129" t="b">
+        <v>1</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12701,7 +12645,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -12714,10 +12658,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S133" t="b">
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -12980,7 +12922,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -12993,10 +12935,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13071,7 +13011,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -13084,10 +13024,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S137" t="b">
+        <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
